--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2216,6 +2216,18 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ヴァルヴレイヴ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>vvv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B151"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2228,6 +2228,18 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ハイビリターン30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>haibireturn30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,6 +2240,18 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>緑ドン</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>midoridon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B153"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2252,18 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ニューパルSP3</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>newpulsp3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2264,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>沖ドキゴージャス25</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>okidokigorgeous25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zettaishogeki4</t>
+          <t>zettaishogeki</t>
         </is>
       </c>
     </row>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2276,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ケロット5</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>kelot5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,6 +2288,18 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>獣王</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>jyuou</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2300,6 +2300,18 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>マイジャグVI</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>myjyaju6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,6 +2312,18 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>モンハンサンブレイク</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>monhunsun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B159"/>
+  <dimension ref="A1:B160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2324,6 +2324,18 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>paripi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B160"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2336,6 +2336,18 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>転生王女と天才令嬢</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>tenseisensai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2348,6 +2348,18 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>海人</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>umintyu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2360,6 +2360,18 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>majicalgirl</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,6 +2372,18 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SAO AGGO</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SAO AGGO_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B164"/>
+  <dimension ref="A1:B165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,6 +2384,18 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>星矢 黄金十二宮</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>seiyaogon_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,6 +2396,18 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ラグナドール</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ragunadool_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,6 +2408,18 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>牙狼</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>garo_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B167"/>
+  <dimension ref="A1:B168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,6 +2420,18 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Vivy</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>vivy_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B168"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,6 +2432,18 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ゴジエヴァ2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>gozieva2_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/masters/machine_image_master.xlsx
+++ b/masters/machine_image_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,6 +2444,18 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ハイハイシオサイRe</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>haisiore_panel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
